--- a/Deliverables/BOM/DigiKey_BOMs/LED_Square_Board_DigiKey.xlsx
+++ b/Deliverables/BOM/DigiKey_BOMs/LED_Square_Board_DigiKey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iftik\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\IbrahimHyder-ReverseEngineering\Deliverables\BOM\DigiKey_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -245,14 +245,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF444444"/>
       <name val="Calibri"/>
@@ -263,6 +255,14 @@
       <u/>
       <sz val="10"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -529,7 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -555,7 +555,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -573,80 +573,64 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -656,8 +640,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -949,52 +943,52 @@
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="54.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="13.42578125" customWidth="1"/>
     <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.5703125" customWidth="1"/>
-    <col min="23" max="23" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="45"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="39"/>
     </row>
     <row r="2" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1067,81 +1061,81 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:40" s="9" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" s="9" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="20">
         <v>10</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="20">
         <f>J3*5</f>
         <v>50</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="20">
         <f>J3*1000</f>
         <v>10000</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="20">
         <f>J3*5000</f>
         <v>50000</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="22">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="P3" s="27">
+      <c r="P3" s="23">
         <f>O3*J3</f>
         <v>0.96</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="22">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="R3" s="27">
+      <c r="R3" s="23">
         <f>Q3*K3</f>
         <v>4.8</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="22">
         <v>2.7029999999999998E-2</v>
       </c>
-      <c r="T3" s="27">
+      <c r="T3" s="23">
         <f>S3*L3</f>
         <v>270.3</v>
       </c>
-      <c r="U3" s="26">
+      <c r="U3" s="22">
         <v>2.01052E-2</v>
       </c>
-      <c r="V3" s="27">
+      <c r="V3" s="23">
         <f>U3*M3</f>
         <v>1005.26</v>
       </c>
-      <c r="W3" s="28"/>
+      <c r="W3" s="42"/>
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3"/>
@@ -1168,10 +1162,10 @@
       <c r="B4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E4" s="10" t="s">
@@ -1180,7 +1174,7 @@
       <c r="F4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="30" t="s">
         <v>38</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -1204,38 +1198,38 @@
         <f>J4*5000</f>
         <v>25000</v>
       </c>
-      <c r="N4" s="38" t="s">
+      <c r="N4" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="32">
         <v>0.1</v>
       </c>
-      <c r="P4" s="40">
+      <c r="P4" s="33">
         <f>O4*J4</f>
         <v>0.5</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="32">
         <v>0.05</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="33">
         <f>Q4*K4</f>
         <v>1.25</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="32">
         <v>6.5599999999999999E-3</v>
       </c>
-      <c r="T4" s="40">
+      <c r="T4" s="33">
         <f>S4*L4</f>
         <v>32.799999999999997</v>
       </c>
       <c r="U4" s="13">
         <v>6.5599999999999999E-3</v>
       </c>
-      <c r="V4" s="41">
+      <c r="V4" s="34">
         <f>U4*M4</f>
         <v>164</v>
       </c>
-      <c r="W4" s="42"/>
+      <c r="W4" s="43"/>
     </row>
     <row r="5" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
@@ -1245,82 +1239,82 @@
       <c r="B5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="27">
         <v>2</v>
       </c>
-      <c r="K5" s="33">
+      <c r="K5" s="28">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L5" s="33">
+      <c r="L5" s="28">
         <f>J5*1000</f>
         <v>2000</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="28">
         <f>J5*5000</f>
         <v>10000</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="31" t="s">
+      <c r="O5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="P5" s="31" t="s">
+      <c r="P5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" s="31" t="s">
+      <c r="Q5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="31" t="s">
+      <c r="R5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="31" t="s">
+      <c r="S5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="T5" s="31" t="s">
+      <c r="T5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="U5" s="31" t="s">
+      <c r="U5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="34" t="s">
+      <c r="W5" s="44" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
       <c r="R6" s="3">
         <f>SUM(R3:R4)</f>
         <v>6.05</v>
@@ -1336,14 +1330,14 @@
       </c>
     </row>
     <row r="7" spans="1:40" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
       <c r="P7" s="2">
         <f>SUM(P3:P4)</f>
         <v>1.46</v>
